--- a/Forecast/Ключи.xlsx
+++ b/Forecast/Ключи.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:S68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,34 +428,34 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Квартал</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Номенклатура.Бренд</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Номенклатура.Артикул </t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Номенклатура.Оригинальный номер</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Номенклатура.Артикул </t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>Номенклатура.Оригинальный номер расширенный</t>
@@ -464,902 +468,1054 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Машина.Двигатель</t>
+          <t>Машина.Бренд</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Машина.Бренд</t>
+          <t>Машина.Модель техники</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Машина.Модель техники</t>
+          <t>Машина.Серия техники</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Машина.Серия техники</t>
+          <t>Лот.CRM год выпуска</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>Серийный номер</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>Лот.CRM наработка</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Документ.Склад</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Количество</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Тип подъемника</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Тип двигателя</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>13.03.2024 13:40:28</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>45654.62438657408</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Ключ зажигания 4130000723001 LGMG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4130000723001</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>4130000723001</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA32J</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>Подъемник ножничный электрический Aurora ASC0808 (RS) гусеничный</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>ASC0808</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ZA32J</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>2253X08T1998</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Минеральные Воды. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>коленчатый</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ножничный</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Электрический</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>28.06.2024 0:00:00</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A3" s="1" t="n">
+        <v>45672.41606481482</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Подъемник ножничный дизельный Zoomlion ZS1623RT</t>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Двигатель дизельный Cummins QSB6.7 (UK) 6.7L - 162 л.с.</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ZS1623RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>BARC023G00017</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>С-Петербург. Ремзона аренды</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ножничный</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>28.06.2024 0:00:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A4" s="1" t="n">
+        <v>45744.51771990741</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA16СRT</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA16CRT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ZA20J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>BARC023G00044</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>С-Петербург. Ремзона аренды</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Калуга. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>28.06.2024 17:32:07</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A5" s="1" t="n">
+        <v>45754.48600694445</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Подъемник ножничный дизельный Zoomlion ZS1623RT</t>
+          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Двигатель дизельный Cummins QSB6.7 (UK) 6.7L - 162 л.с.</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA18CRT2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ZS1623RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>BARC024C00202</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">С-Петербург. Склад Запчасти </t>
+          <t>998</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Самара. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ножничный</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>11.07.2024 11:27:19</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A6" s="1" t="n">
+        <v>45755.68231481482</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ZA20J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>BARC024H00463</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">С-Петербург. Склад Запчасти </t>
+          <t>590</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Казань. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>11.07.2024 12:17:27</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A7" s="1" t="n">
+        <v>45775.45571759259</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA18CRT</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA18CRT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ZA20J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>BARC023G00066</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">С-Петербург. Склад Запчасти </t>
+          <t>1678</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>12.07.2024 17:32:41</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A8" s="1" t="n">
+        <v>45783.69090277778</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый электрический Zoomlion ZA14JE</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ZA14JE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>BARC023G00054</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">С-Петербург. Склад Запчасти </t>
+          <t>1989</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>20.08.2024 15:59:28</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A9" s="1" t="n">
+        <v>45789.43673611111</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA14J</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA18CRT2</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ZA14J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>BARC024C00216</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>24.12.2024 17:29:07</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A10" s="1" t="n">
+        <v>45789.72003472222</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA41RT</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA41RT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BA18CRT2</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>BART024C00045</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Саратов. Сервисное обслуживание. </t>
+          <t>4076</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Череповец  Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10.01.2025 13:05:08</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>45790.38539351852</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA16СRT</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA16CRT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ZA20J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>BARC023G00045</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>376</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10.01.2025 13:21:31</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>45790.46697916667</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Подъемник ножничный электрический Zoomlion ZS1414HD</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ZS1414HD</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>BARM024E00259</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>379</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ножничный</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>15.01.2025 9:59:08</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>45804.50400462963</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1375,145 +1531,169 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA22CRT</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BA22CRT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>BARC023I00234</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>С_Петербург. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>27.03.2025 13:46:28</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>45806.72106481482</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Подъёмник телескопический дизельный Zoomlion ZT26J</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ZT26J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ZT</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>BARM024B00108</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Казань. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>телескопический</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>28.03.2025 12:25:31</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>45814.4418287037</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1529,220 +1709,258 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA16СRT</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>Подъемник мачтовый электрический Dingli AMWP11.5-8100AC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>AMWP11.5-8100AC</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>BA16CRT</t>
+          <t>AMWP</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>MTAM023D00636</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Калуга. Сервисное обслуживание</t>
+          <t>236</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>коленчатый</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>мачтовый</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Электрический</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>31.03.2025 10:06:21</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>45835.69512731482</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Подъемник ножничный электрический Zoomlion ZS1212HD</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>Подъемник коленчатый электрический Dingli BA18NE</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA18NE</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ZS1212HD</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>BAE18NE023D0292</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>558</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>ножничный</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Электрический</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>02.04.2025 18:57:08</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>45855.46695601852</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ZA20J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>BARM023J00070</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>07.04.2025 11:39:51</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>45866.4321412037</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1758,70 +1976,80 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>Подъемник коленчатый электрический Dingli BA18NE</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA18NE</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BA18CRT2</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>BAE18NE023F0538</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Самара. Сервисное обслуживание</t>
+          <t>595</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Электрический</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>08.04.2025 16:22:32</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>45875.54300925926</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1837,145 +2065,169 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BA22CRT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>BARC023I00263</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Казань. Сервисное обслуживание</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>18.04.2025 12:31:08</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>45882.57224537037</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Подъёмник телескопический дизельный Zoomlion ZT26J</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA41RT</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA41RT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ZT26J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ZT</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>BART024C00045</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Череповец  Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>телескопический</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>28.04.2025 10:56:14</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>45895.66660879629</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1991,145 +2243,169 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA18CRT</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BA18CRT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>2561700100R000377</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>28.04.2025 12:47:44</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>45902.44177083333</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый электрический Zoomlion ZA14JE</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA16CRT2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA16CRT2</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ZA14JE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>BARC024B00079</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>811</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>06.05.2025 16:34:54</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>45903.44025462963</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2145,382 +2421,432 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA22CRT</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BA22CRT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>BARM024C00119</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
+          <t>173</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>С_Петербург. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>12.05.2025 9:18:56</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>45903.71244212963</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>Ключ выключения и переключения режимов работы 1020522018</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1020522018</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>1020522018</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Подъемник ножничный электрический Aurora AS0607W(H)</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Zoomlion</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>ZA20J</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>AS0607W</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>2561700100R000498</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>813</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">  Пенза.  Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ножничный</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>12.05.2025 10:28:54</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>45903.71304398148</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ключ-селектор 00006133</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>Ключ выключения и переключения режимов работы 1020522018</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>1020522018</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>1020522018</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Zoomlion</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>ZA20J</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BA18CRT2</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>2561700100R000401</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">  Пенза.  Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>12.05.2025 17:16:51</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>45903.71356481482</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ключ-селектор 00006133</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>Ключ выключения и переключения режимов работы 1020522018</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>1020522018</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>1020522018</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA41RT</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Zoomlion</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>ZA20J</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BA41RT</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>2564700400N000270</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Череповец  Склад Запчастей для Сервиса</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">  Пенза.  Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>13.05.2025 9:14:58</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>45903.71403935185</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ключ-селектор 00006133</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>Ключ выключения и переключения режимов работы 1020522018</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>1020522018</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>1020522018</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA16СRT</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Zoomlion ZA24J</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Zoomlion</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>ZA24J</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BA16CRT</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>2561900700R000198</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>370</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">  Пенза.  Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>13.05.2025 11:12:27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>45904.43055555555</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2536,74 +2862,80 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+          <t>Подъемник коленчатый электрический Dingli BA18NE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA18NE</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>BAE18NE023D0293</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Электрический</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>27.05.2025 12:05:46</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>45904.43055555555</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2619,145 +2951,169 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>Подъемник коленчатый электрический Dingli BA18NE</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA18NE</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>BA22CRT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>BAE18NE023D0293</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Электрический</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>27.05.2025 12:34:49</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>45904.45028935185</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Подъемник ножничный электрический LGMG AS0808</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LGMG</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>AS0808</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>BAR2800023G0425</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Казань. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>ножничный</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>29.05.2025 17:18:20</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>45909.4421412037</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2778,69 +3134,75 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>BARM023J00074</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Казань. Сервисное обслуживание</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПО Запасные части</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>06.06.2025 10:36:14</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>45912.4025925926</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2856,70 +3218,80 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Подъемник мачтовый электрический Dingli AMWP11.5-8100AC</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>AMWP11.5-8100AC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>AMWP</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>BARC024H00462</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>мачтовый</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>27.06.2025 16:40:59</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>45915.72086805556</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2935,70 +3307,80 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый электрический Dingli BA18NE</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BA18NE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>BARM023H00004</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>С_Петербург. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>17.07.2025 11:12:25</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>45917.39026620371</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3019,69 +3401,75 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>BARM024C00118</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
           <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>28.07.2025 10:22:17</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>45933.40542824074</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3097,70 +3485,80 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый электрический Dingli BA18NE</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BA18NE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>2561700100R000377</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>06.08.2025 13:01:56</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>45952.49412037037</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3176,145 +3574,169 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA22CRT</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>BA22CRT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>BART024H00170</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>12.08.2025 11:34:29</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>45952.53200231482</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA32J</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA18CRT2</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ZA32J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>BARC024A00003</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>13.08.2025 13:44:02</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>45952.63375</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3330,145 +3752,169 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA41RT</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>Подъемник ножничный электрический Dingli JCPT1612HA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>JCPT1612HA</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BA41RT</t>
+          <t>JCPT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>JPHA023G06256</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Череповец  Склад Запчастей для Сервиса</t>
+          <t>187</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>коленчатый</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>ножничный</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Электрический</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>26.08.2025 15:25:06</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>45972.41101851852</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ZA20J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>BARM023H00004</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
           <t>С_Петербург. Сервисное обслуживание</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>26.08.2025 15:59:55</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>45973.56703703704</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3484,70 +3930,80 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>BA22CRT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>BARM023H00021</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>02.09.2025 10:36:09</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="1" t="n">
+        <v>45974.43876157407</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3563,70 +4019,80 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA16CRT2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BA16CRT2</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>BARC023G00017</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>03.09.2025 10:33:58</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="A42" s="1" t="n">
+        <v>45974.47224537037</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3642,394 +4108,436 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+          <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>BART024H00170</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>03.09.2025 17:05:55</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="1" t="n">
+        <v>45980.60905092592</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ключ выключения и переключения режимов работы 1020522018</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>Ключ-селектор 00006133</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1020522018</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1020522018</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ZA20J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>BAR2800023G0427</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Пенза.  Склад Запчастей для Сервиса</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>03.09.2025 17:06:47</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="1" t="n">
+        <v>45986.4299537037</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ключ выключения и переключения режимов работы 1020522018</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>Ключ-селектор 00006133</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1020522018</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1020522018</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ZA20J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>BART025C00115</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Пенза.  Склад Запчастей для Сервиса</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>03.09.2025 17:07:32</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="1" t="n">
+        <v>45987.41368055555</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ключ выключения и переключения режимов работы 1020522018</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>Ключ-селектор 00006133</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1020522018</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1020522018</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>Подъемник коленчатый электрический Dingli BA18NE</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA18NE</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ZA20J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>BAE18NE023F0762</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Пенза.  Склад Запчастей для Сервиса</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Нижний Новгород. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Электрический</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>03.09.2025 17:08:13</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="1" t="n">
+        <v>45988.6924074074</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ключ выключения и переключения режимов работы 1020522018</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>Ключ-селектор 00006133</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1020522018</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1020522018</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA24J</t>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Двигатель дизельный CUMMINS QSF2.8t3TC72</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ZA24J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>BAR2800123E0305</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Пенза.  Склад Запчастей для Сервиса</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>04.09.2025 10:20:00</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="A47" s="1" t="n">
+        <v>45988.6924074074</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4045,70 +4553,80 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый электрический Dingli BA18NE</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>BA18NE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BAR2800123E0305</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q47" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>04.09.2025 10:20:00</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="1" t="n">
+        <v>45989.37509259259</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4124,70 +4642,80 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый электрический Dingli BA18NE</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BA18NE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BARM023H00013</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
+          <t>2653</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q48" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>04.09.2025 10:48:25</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="1" t="n">
+        <v>45993.61743055555</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4208,69 +4736,75 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>BARM023J00074</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Казань. Сервисное обслуживание</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>09.09.2025 10:36:41</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="1" t="n">
+        <v>46000.53017361111</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4286,74 +4820,80 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+          <t>Подъемник коленчатый дизельный Dingli BA16CRT2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA16CRT2</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>BARC024B00074</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>ПО Запасные части</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>12.09.2025 9:39:44</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="1" t="n">
+        <v>46001.67763888889</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4369,145 +4909,169 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BA22CRT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>BARM023H00014</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>15.09.2025 16:51:44</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="A52" s="1" t="n">
+        <v>46006.62092592593</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA20J</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA18CRT2</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ZA20J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>BARC024D00312</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>851</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>15.09.2025 17:18:03</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="A53" s="1" t="n">
+        <v>46010.42409722223</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4523,74 +5087,80 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+          <t>Подъемник коленчатый дизельный Sinoboom AB18J</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Sinoboom</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>AB18J</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>402200570</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>202</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>17.09.2025 9:21:59</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="A54" s="1" t="n">
+        <v>46016.36876157407</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4606,74 +5176,80 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA18CRT2</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>BARC024C00215</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>03.10.2025 9:43:49</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="A55" s="1" t="n">
+        <v>46020.49303240741</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4692,67 +5268,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>BA22CRT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>BARC023I00237</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>22.10.2025 11:51:32</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="A56" s="1" t="n">
+        <v>46021.99998842592</v>
+      </c>
+      <c r="B56" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4768,70 +5354,80 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>BARC023G00057</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>22.10.2025 12:46:05</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A57" s="1" t="n">
+        <v>46048.68215277778</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4847,70 +5443,80 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>BA18CRT2</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>BARM024C00113</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Екатеринбург. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>22.10.2025 15:12:36</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A58" s="1" t="n">
+        <v>46050.44313657407</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4926,145 +5532,169 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Подъемник ножничный электрический Dingli JCPT1612HA</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA16CRT2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA16CRT2</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>JCPT1612HA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>JCPT</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>BARC024C00148</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>927</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Уфа. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>ножничный</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>07.11.2025 11:23:45</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A59" s="1" t="n">
+        <v>46055.61380787037</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ключ замка зажигания ZOOMLION</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>НЕОПРЕДЕЛЕН</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>Ключ-селектор 00006133</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>УТ-00005334</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Zoomlion ZA32J</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA16CRT2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Zoomlion</t>
+          <t>BA16CRT2</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ZA32J</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>BARC024B00079</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
+          <t>811</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>11.11.2025 9:51:52</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A60" s="1" t="n">
+        <v>46066.37777777778</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5080,74 +5710,80 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA18CRT2</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>BARC024D00331</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>С_Петербург. Сервисное обслуживание</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>12.11.2025 13:36:32</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A61" s="1" t="n">
+        <v>46066.45535879629</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5163,74 +5799,80 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+          <t>Подъемник коленчатый дизельный Dingli BA16CRT2</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA16CRT2</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>BARC024B00075</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>13.11.2025 10:31:49</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A62" s="1" t="n">
+        <v>46071.44619212963</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5246,70 +5888,80 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA22CRT</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT2 4WS</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT2 4WS</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BA22CRT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>BARC024I00587</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>ПТО СК запчасти для арендного парка</t>
+          <t>581</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Пермь. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>13.11.2025 11:20:02</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A63" s="1" t="n">
+        <v>46071.72607638889</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5325,70 +5977,80 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>BARC024D00335</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
+          <t>734</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>19.11.2025 14:37:02</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A64" s="1" t="n">
+        <v>46072.65207175926</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5409,69 +6071,75 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA28RT</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
+          <t>BAR2800023G0427</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
           <t>2973</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q64" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>25.11.2025 10:19:08</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A65" s="1" t="n">
+        <v>46078.69221064815</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5490,67 +6158,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>BART024K00323</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>С_Петербург. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>26.11.2025 9:55:42</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A66" s="1" t="n">
+        <v>46080.56670138889</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5566,70 +6244,80 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый электрический Dingli BA18NE</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
+          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA18CRT2</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>BA18NE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>BARC024C00155</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Нижний Новгород. Сервисное обслуживание</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Казань. Сервисное обслуживание</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>27.11.2025 16:37:04</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A67" s="1" t="n">
+        <v>46085.35028935185</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5645,74 +6333,80 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA18CRT2</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BARC025D00138</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q67" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>27.11.2025 16:37:04</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A68" s="1" t="n">
+        <v>46086.69871527778</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5728,770 +6422,57 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
+          <t>Подъемник коленчатый дизельный Dingli BA22CRT2 4WS</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>DEUTZ TD2.9L4</t>
+          <t>Dingli</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA22CRT2 4WS</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BA28RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BARC024I00558</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
           <t>коленчатый</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>28.11.2025 9:00:08</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>DEUTZ TD2.9L4</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>BA28RT</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>2653</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>ПТО СК запчасти для арендного парка</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>коленчатый</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>02.12.2025 14:49:06</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>DEUTZ TD2.9L4</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>BA28RT</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>1341</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>ПТО СК запчасти для арендного парка</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>коленчатый</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>09.12.2025 12:43:27</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Подъемник коленчатый дизельный Dingli BA16CRT2</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>BA16CRT2</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>ПТО СК запчасти для арендного парка</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>коленчатый</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>10.12.2025 16:15:48</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Подъемник коленчатый дизельный Dingli BA28RT</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>DEUTZ TD2.9L4</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>BA28RT</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>2259</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>коленчатый</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>15.12.2025 14:54:08</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>BA18CRT2</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>ПТО СК запчасти для арендного парка</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>коленчатый</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>19.12.2025 10:10:42</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Подъемник коленчатый дизельный Sinoboom AB18J</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Sinoboom</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>AB18J</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>ПТО СК запчасти для арендного парка</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>коленчатый</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>25.12.2025 8:51:01</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Подъемник коленчатый дизельный Dingli BA18CRT2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>BA18CRT2</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>1675</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>ПТО СК запчасти для арендного парка</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>коленчатый</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>29.12.2025 11:49:58</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Подъемник коленчатый дизельный Dingli BA22CRT2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>BA22CRT</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>ПТО СК запчасти для арендного парка</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>коленчатый</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>30.12.2025 23:59:59</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Ключ-селектор 00006133</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Подъемник коленчатый дизельный Dingli BA22CRT</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Dingli</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>BA22CRT</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>ПТО СК запчасти для арендного парка</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>коленчатый</t>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
